--- a/docs/Devices.xlsx
+++ b/docs/Devices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AllanK\Desktop\Courses\IV Semester\Statistics\Silicon Showdown\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AllanK\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB53300-D577-4AEE-9144-93B68804A822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD47A3B-448D-479C-A382-03160C0F8B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7120F2FA-3539-4123-B25C-F19AAF0F0EE0}"/>
+    <workbookView xWindow="1776" yWindow="1776" windowWidth="17280" windowHeight="8964" xr2:uid="{7120F2FA-3539-4123-B25C-F19AAF0F0EE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>Allan</t>
   </si>
@@ -59,15 +59,9 @@
     <t>Erfan</t>
   </si>
   <si>
-    <t>Merdanchik</t>
-  </si>
-  <si>
     <t>RTX 4060</t>
   </si>
   <si>
-    <t>Sevil</t>
-  </si>
-  <si>
     <t>Ahmed</t>
   </si>
   <si>
@@ -141,6 +135,24 @@
   </si>
   <si>
     <t>RTX 4070</t>
+  </si>
+  <si>
+    <t>Emir</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>Duygu Cakir</t>
+  </si>
+  <si>
+    <t>M3 …</t>
+  </si>
+  <si>
+    <t>96 GB</t>
+  </si>
+  <si>
+    <t>✅</t>
   </si>
 </sst>
 </file>
@@ -518,13 +530,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E337D42-F98A-4DDD-80BA-EA16F428AD29}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -532,97 +544,118 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -630,32 +663,35 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
         <v>26</v>
       </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -663,18 +699,18 @@
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
